--- a/data/trans_bre/IP16B08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Edad-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,28</t>
+          <t>0,0; 67,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 123,6</t>
+          <t>0,0; 205,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 0,0</t>
+          <t>-60,15; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,8</t>
+          <t>0,0; 48,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 0,0</t>
+          <t>-60,15; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 104,3</t>
+          <t>0,0; 93,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 0,0</t>
+          <t>-43,13; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 0,0</t>
+          <t>-43,13; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 7,14</t>
+          <t>-17,01; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,54</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 7,62</t>
+          <t>-18,25; 7,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Edad-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,28</t>
+          <t>0,0; 66,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 205,61</t>
+          <t>0,0; 199,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 0,0</t>
+          <t>-48,2; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,45</t>
+          <t>0,0; 56,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 0,0</t>
+          <t>-48,2; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 93,97</t>
+          <t>0,0; 130,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 0,0</t>
+          <t>-44,62; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 0,0</t>
+          <t>-44,62; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 6,93</t>
+          <t>-16,63; 7,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 7,38</t>
+          <t>-17,07; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
